--- a/data/data_italy.xlsx
+++ b/data/data_italy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6468b3e9d8abaf9d/MQDE/S2/ESSD/Projet/ESSD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{F13A57C5-3355-9746-AC86-793EBFAD16C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB87E3B8-20B0-41CA-B683-95E575992262}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{F13A57C5-3355-9746-AC86-793EBFAD16C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CFE1E15-F306-4984-96D5-9F31E1F9252B}"/>
   <bookViews>
-    <workbookView xWindow="22965" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8B4CB837-B624-B647-8E85-3149EDD8356C}"/>
+    <workbookView xWindow="2510" yWindow="1830" windowWidth="14400" windowHeight="7280" activeTab="1" xr2:uid="{8B4CB837-B624-B647-8E85-3149EDD8356C}"/>
   </bookViews>
   <sheets>
     <sheet name="Revenues" sheetId="1" r:id="rId1"/>
@@ -327,9 +327,6 @@
     <t>ESI</t>
   </si>
   <si>
-    <t>Total Expenditure</t>
-  </si>
-  <si>
     <t>Total revenue</t>
   </si>
   <si>
@@ -412,6 +409,9 @@
   </si>
   <si>
     <t>BBB+Positive</t>
+  </si>
+  <si>
+    <t>Total expenditure</t>
   </si>
 </sst>
 </file>
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>16</v>
@@ -15633,7 +15633,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>1</v>
@@ -16107,7 +16107,7 @@
         <v>69.599999999999994</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S10" t="str">
         <f t="shared" si="0"/>
@@ -17121,7 +17121,7 @@
         <v>66.5</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S30" t="str">
         <f t="shared" si="0"/>
@@ -17172,7 +17172,7 @@
         <v>66.3</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S31" t="str">
         <f t="shared" si="0"/>
@@ -17529,7 +17529,7 @@
         <v>68.2</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S38" t="str">
         <f t="shared" si="0"/>
@@ -18447,7 +18447,7 @@
         <v>70.2</v>
       </c>
       <c r="Q56" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S56" t="str">
         <f t="shared" si="0"/>
@@ -19008,7 +19008,7 @@
         <v>75.099999999999994</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S67" t="str">
         <f t="shared" ref="S67:S130" si="1">IF(MONTH($A67) = 1, YEAR($A67)&amp;"-Q"&amp;MONTH($A67), IF(MONTH($A67) = 4, YEAR($A67)&amp;"-Q2", IF(MONTH($A67) = 7, YEAR($A67)&amp;"-Q3", IF(MONTH($A67) = 10, YEAR($A67)&amp;"-Q4",""))))</f>
@@ -19110,7 +19110,7 @@
         <v>77.599999999999994</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S69" t="str">
         <f t="shared" si="1"/>
@@ -19263,7 +19263,7 @@
         <v>79.099999999999994</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S72" t="str">
         <f t="shared" si="1"/>
@@ -19569,7 +19569,7 @@
         <v>83.2</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S78" t="str">
         <f t="shared" si="1"/>
@@ -19824,7 +19824,7 @@
         <v>82.1</v>
       </c>
       <c r="Q83" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S83" t="str">
         <f t="shared" si="1"/>
@@ -22629,7 +22629,7 @@
         <v>96.8</v>
       </c>
       <c r="Q138" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S138" t="str">
         <f t="shared" si="2"/>
@@ -22680,7 +22680,7 @@
         <v>95.9</v>
       </c>
       <c r="Q139" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="S139" t="str">
         <f t="shared" si="2"/>
@@ -22833,7 +22833,7 @@
         <v>98.3</v>
       </c>
       <c r="Q142" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S142" t="str">
         <f t="shared" si="2"/>
@@ -22884,7 +22884,7 @@
         <v>100.1</v>
       </c>
       <c r="Q143" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="S143" t="str">
         <f t="shared" si="2"/>
@@ -22935,7 +22935,7 @@
         <v>100.7</v>
       </c>
       <c r="Q144" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S144" t="str">
         <f t="shared" si="2"/>
@@ -22986,7 +22986,7 @@
         <v>102.5</v>
       </c>
       <c r="Q145" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S145" t="str">
         <f t="shared" si="2"/>
@@ -23037,7 +23037,7 @@
         <v>106.5</v>
       </c>
       <c r="Q146" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S146" t="str">
         <f t="shared" si="2"/>
@@ -23088,7 +23088,7 @@
         <v>107.6</v>
       </c>
       <c r="Q147" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S147" t="str">
         <f t="shared" si="2"/>
@@ -23190,7 +23190,7 @@
         <v>111.8</v>
       </c>
       <c r="Q149" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S149" t="str">
         <f t="shared" si="2"/>
@@ -23241,7 +23241,7 @@
         <v>111.6</v>
       </c>
       <c r="Q150" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S150" t="str">
         <f t="shared" si="2"/>
@@ -23343,7 +23343,7 @@
         <v>109.6</v>
       </c>
       <c r="Q152" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="S152" t="str">
         <f t="shared" si="2"/>
@@ -23394,7 +23394,7 @@
         <v>111.7</v>
       </c>
       <c r="Q153" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S153" t="str">
         <f t="shared" si="2"/>
@@ -23751,7 +23751,7 @@
         <v>113.2</v>
       </c>
       <c r="Q160" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S160" t="str">
         <f t="shared" si="2"/>
@@ -23802,7 +23802,7 @@
         <v>110.8</v>
       </c>
       <c r="Q161" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="S161" t="str">
         <f t="shared" si="2"/>
@@ -23853,7 +23853,7 @@
         <v>109</v>
       </c>
       <c r="Q162" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S162" t="str">
         <f t="shared" si="2"/>
@@ -23904,7 +23904,7 @@
         <v>109.3</v>
       </c>
       <c r="Q163" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S163" t="str">
         <f t="shared" si="2"/>
@@ -23955,7 +23955,7 @@
         <v>109.9</v>
       </c>
       <c r="Q164" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S164" t="str">
         <f t="shared" si="2"/>
@@ -24057,7 +24057,7 @@
         <v>111</v>
       </c>
       <c r="Q166" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S166" t="str">
         <f t="shared" si="2"/>
@@ -24108,7 +24108,7 @@
         <v>109.7</v>
       </c>
       <c r="Q167" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S167" t="str">
         <f t="shared" si="2"/>
@@ -24159,7 +24159,7 @@
         <v>108.8</v>
       </c>
       <c r="Q168" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S168" t="str">
         <f t="shared" si="2"/>
@@ -24210,7 +24210,7 @@
         <v>109.5</v>
       </c>
       <c r="Q169" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S169" t="str">
         <f t="shared" si="2"/>
@@ -24261,7 +24261,7 @@
         <v>109.8</v>
       </c>
       <c r="Q170" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S170" t="str">
         <f t="shared" si="2"/>
@@ -24312,7 +24312,7 @@
         <v>109.3</v>
       </c>
       <c r="Q171" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S171" t="str">
         <f t="shared" si="2"/>
@@ -24363,7 +24363,7 @@
         <v>109.1</v>
       </c>
       <c r="Q172" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S172" t="str">
         <f t="shared" si="2"/>
@@ -24414,7 +24414,7 @@
         <v>107.7</v>
       </c>
       <c r="Q173" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S173" t="str">
         <f t="shared" si="2"/>
@@ -24465,7 +24465,7 @@
         <v>107.8</v>
       </c>
       <c r="Q174" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S174" t="str">
         <f t="shared" si="2"/>
@@ -24516,7 +24516,7 @@
         <v>107.9</v>
       </c>
       <c r="Q175" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S175" t="str">
         <f t="shared" si="2"/>
@@ -24567,7 +24567,7 @@
         <v>106.8</v>
       </c>
       <c r="Q176" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S176" t="str">
         <f t="shared" si="2"/>
@@ -24618,7 +24618,7 @@
         <v>106.5</v>
       </c>
       <c r="Q177" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S177" t="str">
         <f t="shared" si="2"/>
@@ -24669,7 +24669,7 @@
         <v>106.1</v>
       </c>
       <c r="Q178" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S178" t="str">
         <f t="shared" si="2"/>
@@ -24720,7 +24720,7 @@
         <v>107</v>
       </c>
       <c r="Q179" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S179" t="str">
         <f t="shared" si="2"/>
@@ -24822,7 +24822,7 @@
         <v>103.7</v>
       </c>
       <c r="Q181" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S181" t="str">
         <f t="shared" si="2"/>
@@ -25332,7 +25332,7 @@
         <v>98.8</v>
       </c>
       <c r="Q191" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S191" t="str">
         <f t="shared" si="2"/>
@@ -25638,7 +25638,7 @@
         <v>92.5</v>
       </c>
       <c r="Q197" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S197" t="str">
         <f t="shared" si="3"/>
@@ -25791,7 +25791,7 @@
         <v>94</v>
       </c>
       <c r="Q200" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S200" t="str">
         <f t="shared" si="3"/>
@@ -25944,7 +25944,7 @@
         <v>95.3</v>
       </c>
       <c r="Q203" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S203" t="str">
         <f t="shared" si="3"/>
@@ -26046,7 +26046,7 @@
         <v>96.1</v>
       </c>
       <c r="Q205" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="S205" t="str">
         <f t="shared" si="3"/>
@@ -26250,7 +26250,7 @@
         <v>99.4</v>
       </c>
       <c r="Q209" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S209" t="str">
         <f t="shared" si="3"/>
@@ -26301,7 +26301,7 @@
         <v>99.1</v>
       </c>
       <c r="Q210" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S210" t="str">
         <f t="shared" si="3"/>
@@ -26352,7 +26352,7 @@
         <v>98.3</v>
       </c>
       <c r="Q211" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S211" t="str">
         <f t="shared" si="3"/>
@@ -26556,7 +26556,7 @@
         <v>99.2</v>
       </c>
       <c r="Q215" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S215" t="str">
         <f t="shared" si="3"/>
@@ -26811,7 +26811,7 @@
         <v>102.4</v>
       </c>
       <c r="Q220" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S220" t="str">
         <f t="shared" si="3"/>
@@ -26964,7 +26964,7 @@
         <v>102.5</v>
       </c>
       <c r="Q223" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S223" t="str">
         <f t="shared" si="3"/>
@@ -27066,7 +27066,7 @@
         <v>105.1</v>
       </c>
       <c r="Q225" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S225" t="str">
         <f t="shared" si="3"/>
@@ -27168,7 +27168,7 @@
         <v>109.4</v>
       </c>
       <c r="Q227" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S227" t="str">
         <f t="shared" si="3"/>
@@ -27270,7 +27270,7 @@
         <v>106.8</v>
       </c>
       <c r="Q229" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S229" t="str">
         <f t="shared" si="3"/>
@@ -27372,7 +27372,7 @@
         <v>107.1</v>
       </c>
       <c r="Q231" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S231" t="str">
         <f t="shared" si="3"/>
@@ -27678,7 +27678,7 @@
         <v>103</v>
       </c>
       <c r="Q237" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S237" t="str">
         <f t="shared" si="3"/>
@@ -27984,7 +27984,7 @@
         <v>103.5</v>
       </c>
       <c r="Q243" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S243" t="str">
         <f t="shared" si="3"/>
@@ -28086,7 +28086,7 @@
         <v>94.8</v>
       </c>
       <c r="Q245" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S245" t="str">
         <f t="shared" si="3"/>
@@ -28137,7 +28137,7 @@
         <v>91.9</v>
       </c>
       <c r="Q246" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S246" t="str">
         <f t="shared" si="3"/>
@@ -28239,7 +28239,7 @@
         <v>92.3</v>
       </c>
       <c r="Q248" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S248" t="str">
         <f t="shared" si="3"/>
@@ -28392,7 +28392,7 @@
         <v>94.9</v>
       </c>
       <c r="Q251" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S251" t="str">
         <f t="shared" si="3"/>
@@ -28443,7 +28443,7 @@
         <v>94.9</v>
       </c>
       <c r="Q252" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S252" t="str">
         <f t="shared" si="3"/>
@@ -28494,7 +28494,7 @@
         <v>96.1</v>
       </c>
       <c r="Q253" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S253" t="str">
         <f t="shared" si="3"/>
@@ -28800,7 +28800,7 @@
         <v>105.4</v>
       </c>
       <c r="Q259" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S259" t="str">
         <f t="shared" ref="S259:S313" si="4">IF(MONTH($A259) = 1, YEAR($A259)&amp;"-Q"&amp;MONTH($A259), IF(MONTH($A259) = 4, YEAR($A259)&amp;"-Q2", IF(MONTH($A259) = 7, YEAR($A259)&amp;"-Q3", IF(MONTH($A259) = 10, YEAR($A259)&amp;"-Q4",""))))</f>
@@ -28902,7 +28902,7 @@
         <v>110.9</v>
       </c>
       <c r="Q261" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S261" t="str">
         <f t="shared" si="4"/>
@@ -29106,7 +29106,7 @@
         <v>124.5</v>
       </c>
       <c r="Q265" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S265" t="str">
         <f t="shared" si="4"/>
@@ -29412,7 +29412,7 @@
         <v>157.19999999999999</v>
       </c>
       <c r="Q271" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S271" t="str">
         <f t="shared" si="4"/>
@@ -29463,7 +29463,7 @@
         <v>157.30000000000001</v>
       </c>
       <c r="Q272" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S272" t="str">
         <f t="shared" si="4"/>
@@ -29514,7 +29514,7 @@
         <v>161.19999999999999</v>
       </c>
       <c r="Q273" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S273" t="str">
         <f t="shared" si="4"/>
@@ -29973,7 +29973,7 @@
         <v>167.2</v>
       </c>
       <c r="Q282" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S282" t="str">
         <f t="shared" si="4"/>
@@ -30075,7 +30075,7 @@
         <v>158.19999999999999</v>
       </c>
       <c r="Q284" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S284" t="str">
         <f t="shared" si="4"/>
@@ -30279,7 +30279,7 @@
         <v>157.9</v>
       </c>
       <c r="Q288" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S288" t="str">
         <f t="shared" si="4"/>
@@ -30585,7 +30585,7 @@
         <v>147.6</v>
       </c>
       <c r="Q294" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S294" t="str">
         <f t="shared" si="4"/>
@@ -30687,7 +30687,7 @@
         <v>151.9</v>
       </c>
       <c r="Q296" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S296" t="str">
         <f t="shared" si="4"/>
@@ -30840,7 +30840,7 @@
         <v>148.80000000000001</v>
       </c>
       <c r="Q299" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S299" t="str">
         <f t="shared" si="4"/>
@@ -31146,7 +31146,7 @@
         <v>147.80000000000001</v>
       </c>
       <c r="Q305" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S305" t="str">
         <f t="shared" si="4"/>
@@ -31197,7 +31197,7 @@
         <v>144.80000000000001</v>
       </c>
       <c r="Q306" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S306" t="str">
         <f t="shared" si="4"/>
@@ -31401,7 +31401,7 @@
         <v>143.69999999999999</v>
       </c>
       <c r="Q310" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S310" t="str">
         <f t="shared" si="4"/>
@@ -31452,7 +31452,7 @@
         <v>142.19999999999999</v>
       </c>
       <c r="Q311" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S311" t="str">
         <f t="shared" si="4"/>
@@ -31503,7 +31503,7 @@
         <v>143.1</v>
       </c>
       <c r="Q312" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S312" t="str">
         <f t="shared" si="4"/>
